--- a/backups/opportunities.xlsx
+++ b/backups/opportunities.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,10 +543,8 @@
           <t>Hyderabads</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="G2" t="n">
+        <v>23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -583,6 +581,70 @@
           <t>[Advait_resume](https://sunfinitytechnologysolution-my.sharepoint.com/:b:/g/personal/tech_support_sunfinity_tech/EQF398s3s9xOkKTUjV81VPoBog2kiUaC51K6-sTMkTNlGw)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OPP000002</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No Job Description Uploaded</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>23LPA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1month</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nowonwonw</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
